--- a/food_beverage_order_forms/026_school_lunch_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/026_school_lunch_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,8 +658,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'grilled_chicken_sandwich',_'value':_1}</t>
+          <t>grilled_chicken_sandwich</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Grilled Chicken Sandwich', 'value': 1}</t>
+          <t>Grilled Chicken Sandwich</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'pizza',_'value':_2}</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Pizza', 'value': 2}</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'salad',_'value':_3}</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Salad', 'value': 3}</t>
+          <t>Salad</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'carrot_sticks',_'value':_1}</t>
+          <t>carrot_sticks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Carrot Sticks', 'value': 1}</t>
+          <t>Carrot Sticks</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'chips',_'value':_2}</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Chips', 'value': 2}</t>
+          <t>Chips</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'apple',_'value':_3}</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Apple', 'value': 3}</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'apple',_'value':_1}</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Apple', 'value': 1}</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'orange',_'value':_2}</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Orange', 'value': 2}</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'cranberry',_'value':_3}</t>
+          <t>cranberry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Cranberry', 'value': 3}</t>
+          <t>Cranberry</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'apple',_'value':_1}</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Apple', 'value': 1}</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'banana',_'value':_2}</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Banana', 'value': 2}</t>
+          <t>Banana</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'grapes',_'value':_3}</t>
+          <t>grapes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Grapes', 'value': 3}</t>
+          <t>Grapes</t>
         </is>
       </c>
     </row>
